--- a/docs/deliverables/out/Drop-0_Setup_and_Data_Migration/TestPlans/BIBS_TestPlan_BRD-11_User_Access_Maintenance_v1.0.xlsx
+++ b/docs/deliverables/out/Drop-0_Setup_and_Data_Migration/TestPlans/BIBS_TestPlan_BRD-11_User_Access_Maintenance_v1.0.xlsx
@@ -2096,7 +2096,7 @@
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Role code and name (and demo user for built BRDs)</t>
+          <t>Role code and name (and SIT/UAT user for built BRDs)</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr"/>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>Demo seed that provides it (built BRDs) or how to prepare it; non-production data is masked</t>
+          <t>Seed that provides it (built BRDs) or how to prepare it; non-production data is masked</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr"/>
@@ -26708,7 +26708,7 @@
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Planned demo seed V1960 (requestor, uamapprover, secapprover) and existing seeds V900 / V980; the others created by the test lead</t>
+          <t>Planned seed V1960 (requestor, uamapprover, secapprover) and existing seeds V900 / V980; the others created by the test lead</t>
         </is>
       </c>
       <c r="E5" s="12" t="n">
@@ -26733,7 +26733,7 @@
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Planned demo seed V1960 of the build design</t>
+          <t>Planned seed V1960 of the build design</t>
         </is>
       </c>
       <c r="E6" s="12" t="n">
